--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N100_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N100_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.20587869977047</v>
+        <v>5.395955288712702</v>
       </c>
       <c r="D2" t="n">
-        <v>33.13006430782913</v>
+        <v>5.383635450022234</v>
       </c>
       <c r="E2" t="n">
-        <v>8.228272127550039</v>
+        <v>1.337094220726881</v>
       </c>
       <c r="F2" t="n">
-        <v>12.00208444873822</v>
+        <v>1.95033872291996</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.28948528646578</v>
+        <v>5.40954135905069</v>
       </c>
       <c r="D3" t="n">
-        <v>31.99761311868566</v>
+        <v>5.19961213178642</v>
       </c>
       <c r="E3" t="n">
-        <v>8.228272127550039</v>
+        <v>1.337094220726881</v>
       </c>
       <c r="F3" t="n">
-        <v>12.00208444873822</v>
+        <v>1.95033872291996</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.88644912306746</v>
+        <v>6.806547982498463</v>
       </c>
       <c r="D4" t="n">
-        <v>40.71311484364566</v>
+        <v>6.615881162092419</v>
       </c>
       <c r="E4" t="n">
-        <v>8.228272127550039</v>
+        <v>1.337094220726881</v>
       </c>
       <c r="F4" t="n">
-        <v>12.00208444873822</v>
+        <v>1.95033872291996</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.46059778810507</v>
+        <v>2.999847140567073</v>
       </c>
       <c r="D5" t="n">
-        <v>18.6560349782248</v>
+        <v>3.03160568396153</v>
       </c>
       <c r="E5" t="n">
-        <v>8.228272127550039</v>
+        <v>1.337094220726881</v>
       </c>
       <c r="F5" t="n">
-        <v>12.00208444873822</v>
+        <v>1.95033872291996</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.85772347966433</v>
+        <v>7.776880065445454</v>
       </c>
       <c r="D6" t="n">
-        <v>51.39727871404625</v>
+        <v>8.352057791032516</v>
       </c>
       <c r="E6" t="n">
-        <v>8.228272127550039</v>
+        <v>1.337094220726881</v>
       </c>
       <c r="F6" t="n">
-        <v>12.00208444873822</v>
+        <v>1.95033872291996</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.52936656932474</v>
+        <v>6.748522067515271</v>
       </c>
       <c r="D7" t="n">
-        <v>44.72450500858271</v>
+        <v>7.267732063894691</v>
       </c>
       <c r="E7" t="n">
-        <v>8.228272127550039</v>
+        <v>1.337094220726881</v>
       </c>
       <c r="F7" t="n">
-        <v>12.00208444873822</v>
+        <v>1.95033872291996</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.25678223257862</v>
+        <v>5.241727112794027</v>
       </c>
       <c r="D8" t="n">
-        <v>57.26216187298429</v>
+        <v>9.305101304359948</v>
       </c>
       <c r="E8" t="n">
-        <v>8.228272127550039</v>
+        <v>1.337094220726881</v>
       </c>
       <c r="F8" t="n">
-        <v>12.00208444873822</v>
+        <v>1.95033872291996</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.55792239125495</v>
+        <v>5.615662388578929</v>
       </c>
       <c r="D9" t="n">
-        <v>52.14293446446053</v>
+        <v>8.473226850474836</v>
       </c>
       <c r="E9" t="n">
-        <v>8.228272127550039</v>
+        <v>1.337094220726881</v>
       </c>
       <c r="F9" t="n">
-        <v>12.00208444873822</v>
+        <v>1.95033872291996</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
